--- a/docs/detail-design/13_PhuThu.xlsx
+++ b/docs/detail-design/13_PhuThu.xlsx
@@ -798,7 +798,7 @@
       <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6905625" cy="5686425"/>
+    <xdr:ext cx="6962775" cy="5734050"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -834,10 +834,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7010400" cy="7419975"/>
+    <xdr:ext cx="7077075" cy="7477125"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -873,10 +873,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6905625" cy="5686425"/>
+    <xdr:ext cx="6962775" cy="5734050"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -2018,7 +2018,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG152"/>
+  <dimension ref="B1:AG154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2133,85 +2133,85 @@
       <c r="AF77" s="4"/>
       <c r="AG77" s="4"/>
     </row>
-    <row r="110" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B110" s="4" t="s">
+    <row r="111" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B111" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="4"/>
-      <c r="L110" s="4"/>
-      <c r="M110" s="4"/>
-      <c r="N110" s="4"/>
-      <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
-      <c r="Q110" s="4"/>
-      <c r="R110" s="4"/>
-      <c r="S110" s="4"/>
-      <c r="T110" s="4"/>
-      <c r="U110" s="4"/>
-      <c r="V110" s="4"/>
-      <c r="W110" s="4"/>
-      <c r="X110" s="4"/>
-      <c r="Y110" s="4"/>
-      <c r="Z110" s="4"/>
-      <c r="AA110" s="4"/>
-      <c r="AB110" s="4"/>
-      <c r="AC110" s="4"/>
-      <c r="AD110" s="4"/>
-      <c r="AE110" s="4"/>
-      <c r="AF110" s="4"/>
-      <c r="AG110" s="4"/>
-    </row>
-    <row r="152" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B152" s="4" t="s">
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="4"/>
+      <c r="T111" s="4"/>
+      <c r="U111" s="4"/>
+      <c r="V111" s="4"/>
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+      <c r="AA111" s="4"/>
+      <c r="AB111" s="4"/>
+      <c r="AC111" s="4"/>
+      <c r="AD111" s="4"/>
+      <c r="AE111" s="4"/>
+      <c r="AF111" s="4"/>
+      <c r="AG111" s="4"/>
+    </row>
+    <row r="154" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B154" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
-      <c r="K152" s="4"/>
-      <c r="L152" s="4"/>
-      <c r="M152" s="4"/>
-      <c r="N152" s="4"/>
-      <c r="O152" s="4"/>
-      <c r="P152" s="4"/>
-      <c r="Q152" s="4"/>
-      <c r="R152" s="4"/>
-      <c r="S152" s="4"/>
-      <c r="T152" s="4"/>
-      <c r="U152" s="4"/>
-      <c r="V152" s="4"/>
-      <c r="W152" s="4"/>
-      <c r="X152" s="4"/>
-      <c r="Y152" s="4"/>
-      <c r="Z152" s="4"/>
-      <c r="AA152" s="4"/>
-      <c r="AB152" s="4"/>
-      <c r="AC152" s="4"/>
-      <c r="AD152" s="4"/>
-      <c r="AE152" s="4"/>
-      <c r="AF152" s="4"/>
-      <c r="AG152" s="4"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+      <c r="L154" s="4"/>
+      <c r="M154" s="4"/>
+      <c r="N154" s="4"/>
+      <c r="O154" s="4"/>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="4"/>
+      <c r="R154" s="4"/>
+      <c r="S154" s="4"/>
+      <c r="T154" s="4"/>
+      <c r="U154" s="4"/>
+      <c r="V154" s="4"/>
+      <c r="W154" s="4"/>
+      <c r="X154" s="4"/>
+      <c r="Y154" s="4"/>
+      <c r="Z154" s="4"/>
+      <c r="AA154" s="4"/>
+      <c r="AB154" s="4"/>
+      <c r="AC154" s="4"/>
+      <c r="AD154" s="4"/>
+      <c r="AE154" s="4"/>
+      <c r="AF154" s="4"/>
+      <c r="AG154" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B42:AG42"/>
     <mergeCell ref="B77:AG77"/>
-    <mergeCell ref="B110:AG110"/>
-    <mergeCell ref="B152:AG152"/>
+    <mergeCell ref="B111:AG111"/>
+    <mergeCell ref="B154:AG154"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>

--- a/docs/detail-design/13_PhuThu.xlsx
+++ b/docs/detail-design/13_PhuThu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="190">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · THÊM / SỬA PHỤ THU</t>
   </si>
@@ -134,6 +134,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Sửa chữ hướng dẫn loại "Thêm tay vào đơn" (chọn khi trả phòng); ô thiếu tô đỏ + hộp lỗi khi lưu; giới hạn độ dài tên.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Thêm phụ thu (mặc định "Ngày trong tuần"), lưu khi chưa chọn ngày</t>
   </si>
   <si>
@@ -395,7 +401,7 @@
     <t>Mức thu (đ/lần)</t>
   </si>
   <si>
-    <t>Không tự cộng. Thực tế chọn ở form Trả phòng (mục "Thêm phụ thu" — file 07); chữ hướng dẫn trong dialog ghi "Khi tạo hoặc sửa đơn" là chưa khớp (đã báo lại).</t>
+    <t>Không tự cộng. Chữ hướng dẫn: "Khi trả phòng, nhân viên đánh dấu phụ thu này ở mục "Thêm phụ thu" để cộng vào." (form Trả phòng — file 07).</t>
   </si>
   <si>
     <t>LOGIC DIALOG PHỤ THU</t>
@@ -485,7 +491,7 @@
     <t>3. Lưu, ẩn</t>
   </si>
   <si>
-    <t>Frontend kiểm tra: tên bắt buộc, khoảng ngày đủ 3 ô (không gửi, không tô đỏ); ≥ 1 ngày (Ngày trong tuần), ≥ 1 khoảng (Khoảng ngày), ≥ 1 hạng → hộp lỗi.</t>
+    <t>Frontend kiểm tra: tên bắt buộc, khoảng ngày đủ 3 ô → tô đỏ ô, hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ)."; ≥ 1 ngày (Ngày trong tuần), ≥ 1 khoảng (Khoảng ngày), ≥ 1 hạng → hộp lỗi. Tên phụ thu, tên dịp tối đa 100 ký tự (maxlength).</t>
   </si>
   <si>
     <t>Gửi { name, whenType, amount (null với Quá giờ), graceMinutes (chỉ Quá giờ, mặc định 15), weekdays, dateRanges, roomTypeIds }. Backend xoá các trường không thuộc loại đang chọn.</t>
@@ -561,6 +567,21 @@
   </si>
   <si>
     <t>Phụ thu không tồn tại</t>
+  </si>
+  <si>
+    <t>Thiếu tên / ô khoảng ngày</t>
+  </si>
+  <si>
+    <t>frontend</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đủ các ô bắt buộc (viền đỏ).</t>
+  </si>
+  <si>
+    <t>Tên quá 100 ký tự (gọi thẳng API)</t>
+  </si>
+  <si>
+    <t>Dữ liệu không hợp lệ — errors.name / errors["dateRanges[i].name"]: "Tối đa 100 ký tự"</t>
   </si>
   <si>
     <t>Lỗi khác</t>
@@ -798,7 +819,7 @@
       <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6962775" cy="5734050"/>
+    <xdr:ext cx="7010400" cy="5772150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -837,7 +858,7 @@
       <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7077075" cy="7477125"/>
+    <xdr:ext cx="7010400" cy="7419975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -873,7 +894,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6962775" cy="5734050"/>
@@ -1236,7 +1257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1967,8 +1988,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -2008,6 +2071,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -2018,7 +2085,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG154"/>
+  <dimension ref="B1:AG153"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2027,7 +2094,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2063,7 +2130,7 @@
     </row>
     <row r="42" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -2099,7 +2166,7 @@
     </row>
     <row r="77" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -2135,7 +2202,7 @@
     </row>
     <row r="111" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B111" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
@@ -2169,41 +2236,41 @@
       <c r="AF111" s="4"/>
       <c r="AG111" s="4"/>
     </row>
-    <row r="154" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B154" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="4"/>
-      <c r="L154" s="4"/>
-      <c r="M154" s="4"/>
-      <c r="N154" s="4"/>
-      <c r="O154" s="4"/>
-      <c r="P154" s="4"/>
-      <c r="Q154" s="4"/>
-      <c r="R154" s="4"/>
-      <c r="S154" s="4"/>
-      <c r="T154" s="4"/>
-      <c r="U154" s="4"/>
-      <c r="V154" s="4"/>
-      <c r="W154" s="4"/>
-      <c r="X154" s="4"/>
-      <c r="Y154" s="4"/>
-      <c r="Z154" s="4"/>
-      <c r="AA154" s="4"/>
-      <c r="AB154" s="4"/>
-      <c r="AC154" s="4"/>
-      <c r="AD154" s="4"/>
-      <c r="AE154" s="4"/>
-      <c r="AF154" s="4"/>
-      <c r="AG154" s="4"/>
+    <row r="153" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B153" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4"/>
+      <c r="O153" s="4"/>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="4"/>
+      <c r="R153" s="4"/>
+      <c r="S153" s="4"/>
+      <c r="T153" s="4"/>
+      <c r="U153" s="4"/>
+      <c r="V153" s="4"/>
+      <c r="W153" s="4"/>
+      <c r="X153" s="4"/>
+      <c r="Y153" s="4"/>
+      <c r="Z153" s="4"/>
+      <c r="AA153" s="4"/>
+      <c r="AB153" s="4"/>
+      <c r="AC153" s="4"/>
+      <c r="AD153" s="4"/>
+      <c r="AE153" s="4"/>
+      <c r="AF153" s="4"/>
+      <c r="AG153" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2211,7 +2278,7 @@
     <mergeCell ref="B42:AG42"/>
     <mergeCell ref="B77:AG77"/>
     <mergeCell ref="B111:AG111"/>
-    <mergeCell ref="B154:AG154"/>
+    <mergeCell ref="B153:AG153"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
@@ -2232,7 +2299,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2268,10 +2335,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2282,22 +2349,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2305,12 +2372,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2323,33 +2390,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2357,12 +2424,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2375,33 +2442,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2409,12 +2476,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2427,33 +2494,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2461,12 +2528,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2479,33 +2546,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2513,12 +2580,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2531,33 +2598,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2565,12 +2632,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2583,33 +2650,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2617,12 +2684,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2635,33 +2702,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2669,12 +2736,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2687,33 +2754,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2721,12 +2788,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2736,7 +2803,7 @@
     </row>
     <row r="12" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -2772,10 +2839,10 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -2786,22 +2853,22 @@
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -2809,12 +2876,12 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
       <c r="AB13" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC13" s="5"/>
       <c r="AD13" s="5"/>
@@ -2827,33 +2894,33 @@
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2861,12 +2928,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2879,33 +2946,33 @@
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -2913,12 +2980,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2928,7 +2995,7 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2964,10 +3031,10 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -2978,22 +3045,22 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P18" s="5"/>
       <c r="Q18" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -3001,12 +3068,12 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
@@ -3019,33 +3086,33 @@
         <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -3053,12 +3120,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -3068,7 +3135,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -3104,10 +3171,10 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -3118,22 +3185,22 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P22" s="5"/>
       <c r="Q22" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -3141,12 +3208,12 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
       <c r="AB22" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
@@ -3159,33 +3226,33 @@
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -3193,12 +3260,12 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -3211,33 +3278,33 @@
         <v>13</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -3245,12 +3312,12 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -3263,33 +3330,33 @@
         <v>14</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3297,12 +3364,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -3312,7 +3379,7 @@
     </row>
     <row r="27" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -3348,10 +3415,10 @@
     </row>
     <row r="28" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -3362,22 +3429,22 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P28" s="5"/>
       <c r="Q28" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R28" s="5"/>
       <c r="S28" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3385,12 +3452,12 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
       <c r="AB28" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC28" s="5"/>
       <c r="AD28" s="5"/>
@@ -3398,38 +3465,38 @@
       <c r="AF28" s="5"/>
       <c r="AG28" s="5"/>
     </row>
-    <row r="29" ht="82" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="29" ht="69" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="6">
         <v>15</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -3437,12 +3504,12 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3627,7 +3694,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG31"/>
+  <dimension ref="B1:AG33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3636,7 +3703,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3672,7 +3739,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3708,10 +3775,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3746,10 +3813,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3784,7 +3851,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3820,14 +3887,14 @@
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -3836,13 +3903,13 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
@@ -3862,14 +3929,14 @@
     </row>
     <row r="8" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -3878,13 +3945,13 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -3904,14 +3971,14 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -3920,13 +3987,13 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -3946,14 +4013,14 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -3962,13 +4029,13 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -3988,14 +4055,14 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -4004,13 +4071,13 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
@@ -4030,14 +4097,14 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -4046,13 +4113,13 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -4072,7 +4139,7 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -4108,7 +4175,7 @@
     </row>
     <row r="15" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -4142,12 +4209,12 @@
       <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="16" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -4182,10 +4249,10 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -4220,10 +4287,10 @@
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -4258,10 +4325,10 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -4296,7 +4363,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -4332,7 +4399,7 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -4346,11 +4413,11 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O22" s="5"/>
       <c r="P22" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
@@ -4372,7 +4439,7 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -4386,11 +4453,11 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -4412,7 +4479,7 @@
     </row>
     <row r="24" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -4426,11 +4493,11 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -4452,7 +4519,7 @@
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -4470,7 +4537,7 @@
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
@@ -4492,7 +4559,7 @@
     </row>
     <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -4510,7 +4577,7 @@
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -4532,7 +4599,7 @@
     </row>
     <row r="27" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4546,11 +4613,11 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
@@ -4572,7 +4639,7 @@
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -4590,7 +4657,7 @@
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -4612,7 +4679,7 @@
     </row>
     <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -4630,7 +4697,7 @@
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -4652,7 +4719,7 @@
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -4670,7 +4737,7 @@
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -4692,7 +4759,7 @@
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -4706,11 +4773,11 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -4730,8 +4797,88 @@
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
     </row>
+    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="6">
+        <v>400</v>
+      </c>
+      <c r="O32" s="6"/>
+      <c r="P32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="72">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:AG2"/>
     <mergeCell ref="C3:AG3"/>
@@ -4798,6 +4945,12 @@
     <mergeCell ref="B31:M31"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="P31:AG31"/>
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="P32:AG32"/>
+    <mergeCell ref="B33:M33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="P33:AG33"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
